--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.6465444159684</v>
+        <v>6.117563467594866</v>
       </c>
       <c r="D2" t="n">
-        <v>37.62911760354845</v>
+        <v>6.114731610576624</v>
       </c>
       <c r="E2" t="n">
-        <v>9.492372961325602</v>
+        <v>1.54251060621541</v>
       </c>
       <c r="F2" t="n">
-        <v>9.38072931026157</v>
+        <v>1.524368512917505</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.95540130333823</v>
+        <v>2.105252711792462</v>
       </c>
       <c r="D3" t="n">
-        <v>12.97336878266288</v>
+        <v>2.108172427182717</v>
       </c>
       <c r="E3" t="n">
-        <v>9.492372961325602</v>
+        <v>1.54251060621541</v>
       </c>
       <c r="F3" t="n">
-        <v>9.38072931026157</v>
+        <v>1.524368512917505</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.06232834839675</v>
+        <v>2.772628356614473</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46707661379256</v>
+        <v>2.838399949741291</v>
       </c>
       <c r="E4" t="n">
-        <v>9.492372961325602</v>
+        <v>1.54251060621541</v>
       </c>
       <c r="F4" t="n">
-        <v>9.38072931026157</v>
+        <v>1.524368512917505</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.76327086540731</v>
+        <v>5.324031515628689</v>
       </c>
       <c r="D5" t="n">
-        <v>32.77827286273502</v>
+        <v>5.32646934019444</v>
       </c>
       <c r="E5" t="n">
-        <v>9.492372961325602</v>
+        <v>1.54251060621541</v>
       </c>
       <c r="F5" t="n">
-        <v>9.38072931026157</v>
+        <v>1.524368512917505</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.3852585729469</v>
+        <v>4.937604518103871</v>
       </c>
       <c r="D6" t="n">
-        <v>30.05824427285852</v>
+        <v>4.88446469433951</v>
       </c>
       <c r="E6" t="n">
-        <v>9.492372961325602</v>
+        <v>1.54251060621541</v>
       </c>
       <c r="F6" t="n">
-        <v>9.38072931026157</v>
+        <v>1.524368512917505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
